--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:10</t>
+    <t xml:space="preserve">2026-09-09 23:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:04</t>
+    <t xml:space="preserve">2026-09-17 14:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:01</t>
+    <t xml:space="preserve">2026-09-23 12:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:30</t>
+    <t xml:space="preserve">2026-10-02 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:12</t>
+    <t xml:space="preserve">2026-10-04 08:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2022_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:53</t>
+    <t xml:space="preserve">2026-10-05 10:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -592,7 +592,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1377104.12</v>
+        <v>1377104.13</v>
       </c>
     </row>
     <row r="3">
@@ -626,7 +626,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1134129.12</v>
+        <v>1134129.13</v>
       </c>
     </row>
     <row r="5">
@@ -643,7 +643,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1088746.12</v>
+        <v>1088746.13</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1067164.62</v>
+        <v>1067164.63</v>
       </c>
     </row>
     <row r="10">
@@ -881,7 +881,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>931260.62</v>
+        <v>931260.63</v>
       </c>
     </row>
     <row r="20">
@@ -1136,7 +1136,7 @@
         <v>2022</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>829019.62</v>
+        <v>829019.63</v>
       </c>
     </row>
     <row r="35">
@@ -1170,7 +1170,7 @@
         <v>2022</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>820204.12</v>
+        <v>820204.13</v>
       </c>
     </row>
     <row r="37">
